--- a/Result/profitability/9928.xlsx
+++ b/Result/profitability/9928.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.34875</v>
+        <v>-0.35625</v>
       </c>
       <c r="N2" t="n">
-        <v>5.83625</v>
+        <v>5.26375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3675</v>
+        <v>-0.35875</v>
       </c>
       <c r="N3" t="n">
-        <v>6.8925</v>
+        <v>6.16</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.365</v>
+        <v>-0.35125</v>
       </c>
       <c r="N4" t="n">
-        <v>6.743749999999999</v>
+        <v>7.0625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-4.15</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8287500000000001</v>
+        <v>-0.82625</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7800000000000002</v>
+        <v>0.65625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.21</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8112500000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96875</v>
+        <v>3.17625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7650000000000001</v>
+        <v>-0.7825000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>5.08875</v>
+        <v>5.456250000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6962500000000001</v>
+        <v>-0.6737500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>8.6525</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.06</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6400000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="N9" t="n">
         <v>11.22375</v>
@@ -1645,7 +1645,7 @@
         <v>-0.23</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6425000000000002</v>
+        <v>-0.6425000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>9.62875</v>
@@ -1772,7 +1772,7 @@
         <v>0.25</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5587500000000002</v>
+        <v>-0.5587500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>12.06</v>
@@ -1899,7 +1899,7 @@
         <v>1.17</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3650000000000002</v>
+        <v>-0.365</v>
       </c>
       <c r="N12" t="n">
         <v>12.36875</v>
@@ -2026,7 +2026,7 @@
         <v>-0.2</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1287499999999999</v>
+        <v>0.12875</v>
       </c>
       <c r="N13" t="n">
         <v>19.79</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9928</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>202</v>
+      </c>
+      <c r="D75" t="n">
+        <v>196</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-36</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-17.92%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.36375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.0175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3529411764705882</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-3.140845070422535</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.01999999999999996</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.05714285714285705</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9900000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2456575682382134</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
